--- a/Analysis/Table1_ADHD_Demographics.xlsx
+++ b/Analysis/Table1_ADHD_Demographics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -616,7 +616,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RT Mean (s)</t>
+          <t>HRT Mean (s)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -653,7 +653,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RT Variability (s)</t>
+          <t>HRT SD (s)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -764,77 +764,188 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sex</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+          <t>Omission Error Rate</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.04 (0.14)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.04 (0.05)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.05 (0.20)</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>χ²(1)=0.49</t>
+          <t>t = -0.45</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.4834</t>
+          <t>0.6572</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>φ=0.07</t>
+          <t>d = -0.09</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   0</t>
+          <t>Commission Error Rate</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>48 (48.5%)</t>
+          <t>0.45 (0.25)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>22 (44.0%)</t>
+          <t>0.55 (0.25)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>26 (53.1%)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+          <t>0.34 (0.20)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>t = 4.49</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>d = 0.90</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Detectability (d')</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2.30 (1.09)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1.90 (1.01)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2.70 (1.04)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>t = -3.92</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0.0002</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>d = -0.79</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>χ²(1) = 0.49</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.4834</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>φ = 0.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   0</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>48 (48.5%)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>22 (44.0%)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>26 (53.1%)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t xml:space="preserve">   1</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>51 (51.5%)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>28 (56.0%)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>23 (46.9%)</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
